--- a/DAF08.xlsx
+++ b/DAF08.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HUONG\Downloads\HK2_2025_2026\Fullstack\CK\BaiNop\d-an-cu-i-k-full-stack-nh-ng-ng-i-xa-l\BaiNoptrcnop\d-an-cu-i-k-full-stack-nh-ng-ng-i-xa-l\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HUONG\Downloads\HK2_2025_2026\Fullstack\CK\BaiNop\d-an-cu-i-k-full-stack-nh-ng-ng-i-xa-l\BaiNopFinal\d-an-cu-i-k-full-stack-nh-ng-ng-i-xa-l\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09377AB-5B37-4452-8171-13D74D3C3FDF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68C6F3F5-0A82-4CC7-AD4F-D152311F2210}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24030" windowHeight="13360" xr2:uid="{6C5FC422-F67A-4121-8150-BF01496D5ECB}"/>
   </bookViews>
@@ -424,7 +424,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -490,13 +490,10 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1011,7 +1008,7 @@
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="26" t="s">
         <v>78</v>
       </c>
       <c r="C1" s="12" t="s">
@@ -1461,7 +1458,7 @@
     </row>
     <row r="22" spans="1:9" ht="39" x14ac:dyDescent="0.35">
       <c r="A22" s="9"/>
-      <c r="B22" s="26" t="s">
+      <c r="B22" s="9" t="s">
         <v>46</v>
       </c>
       <c r="C22" s="9" t="s">
